--- a/data/trans_dic/IP2002-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP2002-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores a los que les han extraído dientes por caries o por otro motivo</t>
+          <t>Menores a los que les han extraído dientes por caries o por otro motivo (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,19; 19,23</t>
+          <t>4,07; 18,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 14,64</t>
+          <t>2,7; 15,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,76; 20,66</t>
+          <t>5,37; 18,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 17,62</t>
+          <t>2,98; 18,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,18; 18,24</t>
+          <t>4,12; 18,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,47; 25,42</t>
+          <t>9,47; 25,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,01; 13,93</t>
+          <t>2,16; 13,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,89; 15,7</t>
+          <t>3,36; 16,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,56; 15,37</t>
+          <t>5,55; 14,86</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,45; 17,22</t>
+          <t>7,32; 17,4</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,04; 13,79</t>
+          <t>4,93; 13,43</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,19; 14,58</t>
+          <t>4,52; 13,75</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,97; 15,33</t>
+          <t>5,89; 15,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,02; 9,05</t>
+          <t>1,41; 8,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 7,46</t>
+          <t>0,67; 7,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 9,63</t>
+          <t>1,52; 9,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,38; 13,11</t>
+          <t>4,95; 14,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 10,78</t>
+          <t>2,47; 10,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,88; 12,39</t>
+          <t>3,49; 12,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,83; 10,12</t>
+          <t>1,73; 10,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,36; 13,17</t>
+          <t>6,09; 12,54</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,86; 8,93</t>
+          <t>2,64; 7,87</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,66; 8,06</t>
+          <t>2,8; 8,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,44; 7,61</t>
+          <t>2,24; 7,92</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 11,85</t>
+          <t>1,17; 11,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 11,6</t>
+          <t>1,08; 10,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,37</t>
+          <t>0,0; 7,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,87; 19,49</t>
+          <t>6,03; 20,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,55</t>
+          <t>0,0; 6,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 9,51</t>
+          <t>1,05; 9,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,5</t>
+          <t>0,0; 4,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,51; 15,38</t>
+          <t>3,7; 14,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 6,65</t>
+          <t>1,51; 6,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 8,32</t>
+          <t>2,09; 8,25</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,05</t>
+          <t>0,0; 3,75</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,91; 14,96</t>
+          <t>6,15; 14,85</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 13,69</t>
+          <t>2,98; 12,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,98; 14,92</t>
+          <t>3,61; 14,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,4; 22,06</t>
+          <t>8,21; 22,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,16</t>
+          <t>0,0; 7,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,23</t>
+          <t>0,0; 5,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 10,08</t>
+          <t>1,63; 10,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 16,67</t>
+          <t>5,09; 17,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,92</t>
+          <t>0,0; 3,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 7,0</t>
+          <t>1,74; 6,65</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,57; 10,1</t>
+          <t>3,5; 9,78</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,68; 17,34</t>
+          <t>8,16; 17,4</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,39</t>
+          <t>0,0; 4,14</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,26; 19,19</t>
+          <t>3,37; 18,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,65; 21,3</t>
+          <t>4,99; 21,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,18</t>
+          <t>0,0; 7,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,59; 19,57</t>
+          <t>4,52; 19,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,52; 22,41</t>
+          <t>5,09; 23,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,7; 21,13</t>
+          <t>4,89; 21,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 11,74</t>
+          <t>1,41; 12,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,43; 15,11</t>
+          <t>2,68; 15,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,84; 16,99</t>
+          <t>5,91; 16,97</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,88; 17,82</t>
+          <t>5,95; 16,64</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,95</t>
+          <t>0,74; 6,96</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,55; 14,32</t>
+          <t>4,57; 13,86</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,18; 10,04</t>
+          <t>1,19; 8,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,53; 15,14</t>
+          <t>1,52; 15,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,84; 23,99</t>
+          <t>6,34; 22,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,42; 12,58</t>
+          <t>1,44; 12,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,49; 16,15</t>
+          <t>4,44; 16,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,25; 22,7</t>
+          <t>5,81; 21,1</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,47; 13,18</t>
+          <t>1,49; 14,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,64; 10,03</t>
+          <t>0,64; 9,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,54; 11,44</t>
+          <t>3,42; 10,99</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,84; 15,41</t>
+          <t>5,45; 15,26</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,11; 15,24</t>
+          <t>5,42; 15,23</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,38; 8,02</t>
+          <t>1,42; 8,81</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,73; 8,05</t>
+          <t>1,73; 8,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,61; 9,74</t>
+          <t>2,34; 9,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,93; 8,05</t>
+          <t>1,98; 7,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,98; 14,67</t>
+          <t>5,91; 15,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,76; 11,29</t>
+          <t>3,75; 11,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,66; 11,25</t>
+          <t>2,52; 9,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,85</t>
+          <t>0,48; 4,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,74; 13,74</t>
+          <t>4,94; 13,81</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,54; 8,48</t>
+          <t>3,39; 8,06</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,3; 8,16</t>
+          <t>3,32; 8,56</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,01</t>
+          <t>1,61; 4,97</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,03; 12,45</t>
+          <t>5,98; 12,5</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,81; 13,22</t>
+          <t>5,59; 13,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,95; 7,01</t>
+          <t>1,98; 7,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,0; 9,09</t>
+          <t>2,92; 9,31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,99</t>
+          <t>0,59; 6,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,12; 13,86</t>
+          <t>6,32; 14,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,51; 7,94</t>
+          <t>2,68; 7,83</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,24; 7,74</t>
+          <t>2,16; 7,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,6</t>
+          <t>0,46; 4,63</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,76; 12,1</t>
+          <t>6,59; 12,3</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,77; 6,25</t>
+          <t>2,83; 6,74</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,21; 7,22</t>
+          <t>3,0; 7,15</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,56</t>
+          <t>0,76; 3,76</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,56; 8,91</t>
+          <t>5,52; 8,84</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,12; 6,99</t>
+          <t>4,13; 7,21</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,76; 7,84</t>
+          <t>4,77; 7,97</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,4; 7,6</t>
+          <t>4,46; 7,77</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,91; 9,2</t>
+          <t>5,89; 9,02</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,35; 8,66</t>
+          <t>5,41; 8,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,63; 6,27</t>
+          <t>3,73; 6,43</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,66; 6,7</t>
+          <t>3,73; 6,71</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,16; 8,36</t>
+          <t>6,05; 8,42</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5,23; 7,39</t>
+          <t>5,23; 7,42</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4,55; 6,56</t>
+          <t>4,54; 6,62</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,43; 6,73</t>
+          <t>4,43; 6,64</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores a los que les han extraído dientes por caries o por otro motivo (tasa de respuesta: 99,83%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>4667</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3611</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6133</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5553</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5301</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>9874</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3873</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>6244</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>9968</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>13484</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>10006</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>11797</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1961; 8951</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1468; 8288</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2955; 10304</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2172; 13581</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2226; 9958</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5754; 15572</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1320; 8445</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2585; 12652</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>5676; 15193</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>8432; 20048</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5728; 15591</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>6773; 20603</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>9532</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4014</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2900</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5719</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>8534</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5558</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>7396</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>5446</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>18065</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>9572</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>10296</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>11164</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>5589; 14776</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1352; 8164</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>662; 7262</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1913; 11620</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>5220; 14916</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2483; 11005</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>3733; 13249</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2156; 12683</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>12207; 25113</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>5197; 15469</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5766; 16784</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>5612; 19817</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>3018</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2909</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6687</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1243</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2744</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>5048</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>4262</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>5653</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>1506</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>11735</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>752; 7059</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>679; 6574</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4843</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3426; 11370</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4112</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>697; 6318</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2876</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2424; 9766</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1976; 8658</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2705; 10665</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4761</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>7529; 18173</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>4666</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5887</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>10378</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>935</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>3604</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>7477</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>530</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>5479</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>9492</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>17854</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1465</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2104; 9010</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2659; 10391</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>5977; 16287</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5307</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4584</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1293; 8464</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>3956; 13939</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2531</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>2579; 9829</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>5363; 14970</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>12279; 26186</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5983</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>3432</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4328</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3588</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>5205</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>4963</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1883</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2816</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>8638</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>9291</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>2511</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>6404</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1343; 7568</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2090; 8817</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3191</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1547; 6812</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2174; 10215</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2211; 9872</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>601; 5144</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1089; 6173</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>4884; 14027</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>5184; 14490</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>618; 5814</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>3421; 10381</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2942</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2060</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>5181</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>6823</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>3161</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1794</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>7201</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>9765</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>9830</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>3855</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>636; 4790</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>746; 7593</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>3240; 11674</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>632; 5599</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2534; 9676</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>3191; 11582</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>803; 7629</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>349; 5089</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>3777; 12140</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>5670; 15867</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>5692; 15999</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>1389; 8636</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>4986</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>6730</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>5400</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>11924</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>8858</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>7216</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2381</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>13175</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>13844</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>13946</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>7781</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>25099</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>2136; 10076</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2980; 11854</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2574; 10344</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>7305; 18642</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>4737; 14238</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>3292; 12685</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>648; 6230</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>7644; 21388</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>8466; 20123</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>8567; 22102</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>4256; 13102</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>16648; 34796</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>13501</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>6251</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>7989</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2384</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>14743</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>7901</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>6876</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>2465</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>28243</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>14153</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>14865</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>4849</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>8433; 20586</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>3123; 11151</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>4353; 13861</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>771; 7821</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>9828; 22322</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>4410; 12888</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>3427; 12500</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>708; 7187</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>20204; 37689</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>9128; 21738</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>9228; 22015</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>2180; 10729</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>45821</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>36672</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>40933</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>38849</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>49879</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>48684</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>33716</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>37518</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>95700</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>85356</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>74649</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>76367</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>35622; 57038</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>27367; 47763</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>31401; 52486</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>29229; 51005</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>40380; 61774</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>38044; 60920</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>26153; 45040</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>27882; 50173</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>80403; 111998</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>71459; 101364</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>61774; 90001</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>62221; 93246</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2002-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP2002-Provincia-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,07; 18,56</t>
+          <t>4,16; 19,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,7; 15,22</t>
+          <t>2,36; 14,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,37; 18,71</t>
+          <t>4,73; 19,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,98; 18,64</t>
+          <t>2,99; 17,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,12; 18,43</t>
+          <t>4,12; 17,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,47; 25,62</t>
+          <t>9,65; 25,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,16; 13,84</t>
+          <t>2,05; 14,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,36; 16,43</t>
+          <t>3,53; 16,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,55; 14,86</t>
+          <t>5,49; 15,2</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,32; 17,4</t>
+          <t>7,41; 17,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,93; 13,43</t>
+          <t>5,11; 13,78</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,52; 13,75</t>
+          <t>4,21; 13,56</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,89; 15,58</t>
+          <t>5,97; 15,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,41; 8,51</t>
+          <t>1,39; 8,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 7,33</t>
+          <t>0,67; 6,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,52; 9,25</t>
+          <t>1,25; 9,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,95; 14,14</t>
+          <t>4,37; 13,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,47; 10,93</t>
+          <t>2,58; 11,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,49; 12,37</t>
+          <t>3,57; 12,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 10,17</t>
+          <t>1,82; 10,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,09; 12,54</t>
+          <t>6,41; 12,86</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,64; 7,87</t>
+          <t>2,57; 8,19</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,8; 8,14</t>
+          <t>2,87; 8,08</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,24; 7,92</t>
+          <t>2,24; 7,74</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 11,03</t>
+          <t>1,23; 10,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 10,47</t>
+          <t>1,08; 10,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,92</t>
+          <t>0,0; 7,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,03; 20,02</t>
+          <t>6,18; 19,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,18</t>
+          <t>0,0; 5,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 9,51</t>
+          <t>1,09; 10,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,36</t>
+          <t>0,0; 5,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,7; 14,9</t>
+          <t>3,32; 15,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 6,63</t>
+          <t>1,21; 7,03</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 8,25</t>
+          <t>1,9; 7,83</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,75</t>
+          <t>0,0; 4,08</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,15; 14,85</t>
+          <t>5,89; 15,09</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,98; 12,75</t>
+          <t>2,68; 12,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,61; 14,13</t>
+          <t>3,86; 14,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,21; 22,38</t>
+          <t>8,53; 22,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,67</t>
+          <t>0,0; 7,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,94</t>
+          <t>0,0; 5,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 10,65</t>
+          <t>1,6; 10,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,09; 17,92</t>
+          <t>5,15; 16,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,36</t>
+          <t>0,0; 3,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 6,65</t>
+          <t>1,9; 7,17</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,5; 9,78</t>
+          <t>3,42; 10,14</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,16; 17,4</t>
+          <t>7,8; 16,86</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,14</t>
+          <t>0,0; 3,9</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,37; 18,96</t>
+          <t>3,31; 17,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,99; 21,06</t>
+          <t>3,46; 21,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,79</t>
+          <t>0,0; 9,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,52; 19,92</t>
+          <t>4,49; 20,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,09; 23,9</t>
+          <t>5,03; 22,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,89; 21,82</t>
+          <t>4,46; 19,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,41; 12,08</t>
+          <t>1,41; 11,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,68; 15,16</t>
+          <t>2,51; 14,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,91; 16,97</t>
+          <t>5,85; 18,04</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,95; 16,64</t>
+          <t>6,34; 17,76</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,96</t>
+          <t>0,74; 6,99</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,57; 13,86</t>
+          <t>4,79; 14,49</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,19; 8,97</t>
+          <t>1,19; 10,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,52; 15,47</t>
+          <t>1,5; 14,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,34; 22,83</t>
+          <t>6,91; 23,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,44; 12,75</t>
+          <t>1,41; 12,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,44; 16,94</t>
+          <t>3,87; 16,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,81; 21,1</t>
+          <t>6,45; 21,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,49; 14,15</t>
+          <t>1,44; 13,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,64; 9,4</t>
+          <t>0,66; 9,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,42; 10,99</t>
+          <t>3,54; 11,25</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,45; 15,26</t>
+          <t>5,42; 15,48</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,42; 15,23</t>
+          <t>5,1; 15,25</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,42; 8,81</t>
+          <t>1,41; 8,2</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,73; 8,18</t>
+          <t>1,7; 7,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,34; 9,29</t>
+          <t>2,38; 9,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,98; 7,97</t>
+          <t>1,93; 7,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,91; 15,09</t>
+          <t>5,29; 14,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,75; 11,26</t>
+          <t>3,75; 12,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,52; 9,72</t>
+          <t>2,44; 9,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,66</t>
+          <t>0,49; 5,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,94; 13,81</t>
+          <t>4,47; 14,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,39; 8,06</t>
+          <t>3,52; 8,44</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,32; 8,56</t>
+          <t>3,4; 8,4</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,97</t>
+          <t>1,56; 4,94</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,98; 12,5</t>
+          <t>6,24; 12,76</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,59; 13,64</t>
+          <t>5,66; 13,32</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,98; 7,07</t>
+          <t>2,0; 6,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,92; 9,31</t>
+          <t>2,86; 9,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,59; 6,02</t>
+          <t>0,57; 4,95</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,32; 14,36</t>
+          <t>6,54; 14,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,68; 7,83</t>
+          <t>2,75; 8,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,16; 7,87</t>
+          <t>2,17; 7,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,63</t>
+          <t>0,46; 4,32</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,59; 12,3</t>
+          <t>6,74; 12,31</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,83; 6,74</t>
+          <t>2,8; 6,52</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,0; 7,15</t>
+          <t>3,23; 7,26</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,76</t>
+          <t>0,75; 3,49</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,52; 8,84</t>
+          <t>5,64; 9,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,13; 7,21</t>
+          <t>4,28; 7,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,77; 7,97</t>
+          <t>4,73; 7,91</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,46; 7,77</t>
+          <t>4,34; 7,65</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,89; 9,02</t>
+          <t>5,87; 9,18</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,41; 8,67</t>
+          <t>5,48; 8,57</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,73; 6,43</t>
+          <t>3,61; 6,36</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,73; 6,71</t>
+          <t>3,66; 6,68</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,05; 8,42</t>
+          <t>6,12; 8,33</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5,23; 7,42</t>
+          <t>5,26; 7,55</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4,54; 6,62</t>
+          <t>4,51; 6,56</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,43; 6,64</t>
+          <t>4,39; 6,6</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1961; 8951</t>
+          <t>2006; 9304</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1468; 8288</t>
+          <t>1282; 7876</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2955; 10304</t>
+          <t>2605; 10685</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2172; 13581</t>
+          <t>2181; 12508</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2226; 9958</t>
+          <t>2224; 9596</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5754; 15572</t>
+          <t>5865; 15346</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1320; 8445</t>
+          <t>1252; 8715</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2585; 12652</t>
+          <t>2721; 12473</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5676; 15193</t>
+          <t>5615; 15545</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8432; 20048</t>
+          <t>8536; 20360</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5728; 15591</t>
+          <t>5931; 15997</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6773; 20603</t>
+          <t>6308; 20325</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5589; 14776</t>
+          <t>5656; 14917</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1352; 8164</t>
+          <t>1338; 8149</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>662; 7262</t>
+          <t>662; 6843</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1913; 11620</t>
+          <t>1568; 12144</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5220; 14916</t>
+          <t>4606; 14300</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2483; 11005</t>
+          <t>2601; 11668</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3733; 13249</t>
+          <t>3824; 12927</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2156; 12683</t>
+          <t>2270; 13441</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12207; 25113</t>
+          <t>12851; 25772</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5197; 15469</t>
+          <t>5045; 16098</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5766; 16784</t>
+          <t>5925; 16659</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5612; 19817</t>
+          <t>5618; 19371</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>752; 7059</t>
+          <t>787; 6872</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>679; 6574</t>
+          <t>680; 6571</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4843</t>
+          <t>0; 4722</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3426; 11370</t>
+          <t>3509; 11289</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4112</t>
+          <t>0; 3761</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>697; 6318</t>
+          <t>727; 6799</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2876</t>
+          <t>0; 3755</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2424; 9766</t>
+          <t>2179; 9867</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1976; 8658</t>
+          <t>1585; 9175</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2705; 10665</t>
+          <t>2461; 10124</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 4761</t>
+          <t>0; 5182</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7529; 18173</t>
+          <t>7210; 18467</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2104; 9010</t>
+          <t>1890; 8942</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2659; 10391</t>
+          <t>2841; 10483</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5977; 16287</t>
+          <t>6208; 16537</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 5307</t>
+          <t>0; 5357</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4584</t>
+          <t>0; 4227</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1293; 8464</t>
+          <t>1271; 7992</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3956; 13939</t>
+          <t>4004; 13121</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 2531</t>
+          <t>0; 2895</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2579; 9829</t>
+          <t>2813; 10605</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5363; 14970</t>
+          <t>5239; 15522</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12279; 26186</t>
+          <t>11739; 25377</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 5983</t>
+          <t>0; 5632</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1343; 7568</t>
+          <t>1322; 6942</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2090; 8817</t>
+          <t>1447; 8831</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3191</t>
+          <t>0; 3804</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1547; 6812</t>
+          <t>1535; 7042</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2174; 10215</t>
+          <t>2149; 9506</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2211; 9872</t>
+          <t>2018; 8895</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>601; 5144</t>
+          <t>601; 5055</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1089; 6173</t>
+          <t>1023; 5942</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4884; 14027</t>
+          <t>4836; 14906</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5184; 14490</t>
+          <t>5524; 15466</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>618; 5814</t>
+          <t>619; 5836</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3421; 10381</t>
+          <t>3588; 10856</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>636; 4790</t>
+          <t>635; 5428</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>746; 7593</t>
+          <t>735; 7094</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3240; 11674</t>
+          <t>3533; 12099</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>632; 5599</t>
+          <t>619; 5592</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2534; 9676</t>
+          <t>2208; 9453</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3191; 11582</t>
+          <t>3542; 11870</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>803; 7629</t>
+          <t>778; 7142</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>349; 5089</t>
+          <t>360; 5368</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3777; 12140</t>
+          <t>3912; 12434</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5670; 15867</t>
+          <t>5634; 16089</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5692; 15999</t>
+          <t>5356; 16017</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1389; 8636</t>
+          <t>1387; 8046</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2136; 10076</t>
+          <t>2094; 9493</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2980; 11854</t>
+          <t>3031; 11835</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2574; 10344</t>
+          <t>2506; 10367</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7305; 18642</t>
+          <t>6535; 18397</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4737; 14238</t>
+          <t>4744; 15304</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3292; 12685</t>
+          <t>3192; 12598</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>648; 6230</t>
+          <t>655; 6740</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>7644; 21388</t>
+          <t>6924; 21737</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8466; 20123</t>
+          <t>8779; 21069</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8567; 22102</t>
+          <t>8774; 21689</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4256; 13102</t>
+          <t>4104; 13029</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>16648; 34796</t>
+          <t>17367; 35521</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>8433; 20586</t>
+          <t>8545; 20101</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3123; 11151</t>
+          <t>3157; 10740</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4353; 13861</t>
+          <t>4254; 13778</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>771; 7821</t>
+          <t>740; 6434</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>9828; 22322</t>
+          <t>10162; 22248</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4410; 12888</t>
+          <t>4536; 13391</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3427; 12500</t>
+          <t>3440; 12130</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>708; 7187</t>
+          <t>713; 6707</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>20204; 37689</t>
+          <t>20657; 37701</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>9128; 21738</t>
+          <t>9017; 21007</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>9228; 22015</t>
+          <t>9938; 22333</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2180; 10729</t>
+          <t>2139; 9944</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>35622; 57038</t>
+          <t>36410; 58466</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>27367; 47763</t>
+          <t>28359; 47592</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>31401; 52486</t>
+          <t>31165; 52117</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>29229; 51005</t>
+          <t>28474; 50197</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>40380; 61774</t>
+          <t>40242; 62884</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>38044; 60920</t>
+          <t>38542; 60200</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26153; 45040</t>
+          <t>25286; 44593</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>27882; 50173</t>
+          <t>27386; 49894</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>80403; 111998</t>
+          <t>81343; 110831</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>71459; 101364</t>
+          <t>71872; 103048</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>61774; 90001</t>
+          <t>61321; 89220</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>62221; 93246</t>
+          <t>61602; 92702</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2002-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP2002-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9,81%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16,25%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6,35%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8,86%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>9,68%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6,63%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>11,14%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7,62%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9,81%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>16,25%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,35%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,16; 19,29</t>
+          <t>4,18; 18,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,36; 14,47</t>
+          <t>9,47; 25,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,73; 19,4</t>
+          <t>2,01; 13,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,99; 17,17</t>
+          <t>3,24; 17,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,12; 17,76</t>
+          <t>4,19; 19,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,65; 25,25</t>
+          <t>2,43; 14,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,05; 14,29</t>
+          <t>5,76; 20,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,53; 16,2</t>
+          <t>2,42; 13,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,49; 15,2</t>
+          <t>5,56; 15,37</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,41; 17,67</t>
+          <t>7,45; 17,22</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,11; 13,78</t>
+          <t>5,04; 13,79</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,21; 13,56</t>
+          <t>4,3; 14,37</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8,09%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5,52%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6,91%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4,23%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>10,05%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>4,18%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,93%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>8,09%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,52%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>6,91%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,97; 15,73</t>
+          <t>4,38; 13,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 8,49</t>
+          <t>1,99; 10,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 6,91</t>
+          <t>3,88; 12,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 9,67</t>
+          <t>1,66; 9,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,37; 13,55</t>
+          <t>5,97; 15,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,58; 11,59</t>
+          <t>2,02; 9,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,57; 12,07</t>
+          <t>1,0; 7,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 10,78</t>
+          <t>2,46; 11,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,41; 12,86</t>
+          <t>6,36; 13,17</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,57; 8,19</t>
+          <t>2,86; 8,93</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 8,08</t>
+          <t>2,66; 8,06</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,24; 7,74</t>
+          <t>2,89; 8,42</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4,13%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7,27%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>4,72%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4,63%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1,37%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11,77%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,13%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 10,74</t>
+          <t>0,0; 6,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 10,46</t>
+          <t>0,99; 9,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,73</t>
+          <t>0,0; 4,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,18; 19,88</t>
+          <t>3,38; 14,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,65</t>
+          <t>1,22; 11,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 10,24</t>
+          <t>1,42; 11,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,69</t>
+          <t>0,0; 7,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 15,05</t>
+          <t>5,92; 19,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 7,03</t>
+          <t>1,15; 6,65</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,9; 7,83</t>
+          <t>2,12; 8,32</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,08</t>
+          <t>0,0; 4,05</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,89; 15,09</t>
+          <t>5,85; 14,69</t>
         </is>
       </c>
     </row>
@@ -1069,44 +1069,44 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4,54%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9,61%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>6,6%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>8,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>14,26%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>1,35%</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,54%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,61%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3,71%</t>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,68; 12,65</t>
+          <t>0,0; 5,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,86; 14,25</t>
+          <t>1,62; 10,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,53; 22,73</t>
+          <t>4,57; 16,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,74</t>
+          <t>0,0; 3,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,48</t>
+          <t>2,91; 13,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 10,06</t>
+          <t>3,98; 14,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,15; 16,87</t>
+          <t>8,4; 22,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,84</t>
+          <t>0,0; 7,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,9; 7,17</t>
+          <t>1,72; 7,0</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 10,14</t>
+          <t>3,57; 10,1</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,8; 16,86</t>
+          <t>7,68; 17,34</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,9</t>
+          <t>0,0; 3,48</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>12,18%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10,97%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4,42%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>7,39%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>8,6%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>10,34%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,53%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>10,49%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>12,18%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>10,97%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,31; 17,4</t>
+          <t>5,52; 22,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,46; 21,1</t>
+          <t>4,7; 21,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,29</t>
+          <t>1,4; 11,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,49; 20,59</t>
+          <t>2,69; 15,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,03; 22,24</t>
+          <t>3,26; 19,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,46; 19,66</t>
+          <t>3,65; 21,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,41; 11,87</t>
+          <t>0,0; 8,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,51; 14,59</t>
+          <t>4,74; 20,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,85; 18,04</t>
+          <t>5,84; 16,99</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,34; 17,76</t>
+          <t>5,88; 17,82</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,99</t>
+          <t>0,74; 6,95</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,79; 14,49</t>
+          <t>4,87; 14,98</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>9,07%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>12,43%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5,86%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>3,78%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>5,99%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>13,04%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>9,07%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>12,43%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>5,86%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,19; 10,17</t>
+          <t>3,49; 16,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,5; 14,46</t>
+          <t>6,25; 22,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,91; 23,66</t>
+          <t>1,47; 13,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,41; 12,73</t>
+          <t>0,51; 9,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,87; 16,55</t>
+          <t>1,18; 10,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,45; 21,63</t>
+          <t>1,53; 15,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,44; 13,25</t>
+          <t>6,84; 23,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,66; 9,91</t>
+          <t>1,54; 13,94</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,54; 11,25</t>
+          <t>3,54; 11,44</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,42; 15,48</t>
+          <t>4,84; 15,41</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,1; 15,25</t>
+          <t>5,11; 15,24</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,41; 8,2</t>
+          <t>1,38; 8,09</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7,01%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5,53%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8,96%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>4,05%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>5,28%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>4,16%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>9,65%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7,01%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,53%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,7; 7,71</t>
+          <t>3,76; 11,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,38; 9,28</t>
+          <t>2,66; 11,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,93; 7,98</t>
+          <t>0,48; 4,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,29; 14,89</t>
+          <t>4,96; 14,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,75; 12,11</t>
+          <t>1,73; 8,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,44; 9,65</t>
+          <t>2,61; 9,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 5,04</t>
+          <t>1,93; 8,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,47; 14,04</t>
+          <t>6,18; 15,21</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,52; 8,44</t>
+          <t>3,54; 8,48</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,4; 8,4</t>
+          <t>3,3; 8,16</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,94</t>
+          <t>1,43; 5,01</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,24; 12,76</t>
+          <t>6,36; 13,17</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>9,48%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4,33%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>8,95%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>3,97%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>5,36%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>9,48%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>4,33%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,66; 13,32</t>
+          <t>6,12; 13,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,0; 6,81</t>
+          <t>2,51; 7,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,86; 9,25</t>
+          <t>2,24; 7,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,95</t>
+          <t>0,4; 4,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,54; 14,31</t>
+          <t>5,81; 13,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,75; 8,13</t>
+          <t>1,95; 7,01</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,17; 7,64</t>
+          <t>3,0; 9,09</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,32</t>
+          <t>0,0; 5,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,74; 12,31</t>
+          <t>6,76; 12,1</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,8; 6,52</t>
+          <t>2,77; 6,25</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,23; 7,26</t>
+          <t>3,21; 7,22</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,49</t>
+          <t>0,6; 3,5</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>7,28%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>6,93%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>7,1%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>5,53%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>6,21%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5,92%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>7,28%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>6,93%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>4,81%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,64; 9,06</t>
+          <t>5,91; 9,2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,28; 7,18</t>
+          <t>5,35; 8,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,73; 7,91</t>
+          <t>3,63; 6,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,34; 7,65</t>
+          <t>3,6; 6,68</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,87; 9,18</t>
+          <t>5,56; 8,91</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,48; 8,57</t>
+          <t>4,12; 6,99</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,61; 6,36</t>
+          <t>4,76; 7,84</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,66; 6,68</t>
+          <t>4,59; 7,92</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,12; 8,33</t>
+          <t>6,16; 8,36</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5,26; 7,55</t>
+          <t>5,23; 7,39</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4,51; 6,56</t>
+          <t>4,55; 6,56</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,39; 6,6</t>
+          <t>4,56; 6,81</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2078,37 +2078,37 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5301</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9874</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3873</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5514</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>4667</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>3611</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>6133</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5553</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>5301</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>9874</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>3873</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6244</t>
+          <t>3895</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11797</t>
+          <t>9409</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2006; 9304</t>
+          <t>2260; 9858</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1282; 7876</t>
+          <t>5757; 15450</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2605; 10685</t>
+          <t>1228; 8494</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2181; 12508</t>
+          <t>2017; 10755</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2224; 9596</t>
+          <t>2020; 9273</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5865; 15346</t>
+          <t>1324; 7969</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1252; 8715</t>
+          <t>3173; 11378</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2721; 12473</t>
+          <t>1360; 7585</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5615; 15545</t>
+          <t>5684; 15721</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8536; 20360</t>
+          <t>8579; 19838</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5931; 15997</t>
+          <t>5846; 16004</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6308; 20325</t>
+          <t>5086; 17016</t>
         </is>
       </c>
     </row>
@@ -2281,37 +2281,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8534</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5558</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7396</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4804</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>9532</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4014</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2900</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5719</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8534</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5558</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7396</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5446</t>
+          <t>6042</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11164</t>
+          <t>10846</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5656; 14917</t>
+          <t>4617; 13832</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1338; 8149</t>
+          <t>2002; 10848</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>662; 6843</t>
+          <t>4156; 13263</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1568; 12144</t>
+          <t>1885; 11119</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4606; 14300</t>
+          <t>5660; 14532</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2601; 11668</t>
+          <t>1939; 8690</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3824; 12927</t>
+          <t>992; 7392</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2270; 13441</t>
+          <t>2448; 11755</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12851; 25772</t>
+          <t>12749; 26376</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5045; 16098</t>
+          <t>5632; 17549</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5925; 16659</t>
+          <t>5473; 16622</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5618; 19371</t>
+          <t>6164; 17939</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1243</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2744</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4223</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>3018</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2909</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>836</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6687</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1243</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2744</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>670</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11735</t>
+          <t>10740</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>787; 6872</t>
+          <t>0; 4361</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>680; 6571</t>
+          <t>655; 6319</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4722</t>
+          <t>0; 2969</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3509; 11289</t>
+          <t>1962; 8571</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3761</t>
+          <t>783; 7587</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>727; 6799</t>
+          <t>892; 7286</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3755</t>
+          <t>0; 4504</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2179; 9867</t>
+          <t>3271; 10786</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1585; 9175</t>
+          <t>1497; 8682</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2461; 10124</t>
+          <t>2744; 10754</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 5182</t>
+          <t>0; 5151</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7210; 18467</t>
+          <t>6625; 16645</t>
         </is>
       </c>
     </row>
@@ -2697,37 +2697,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3604</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7477</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>4666</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>5887</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>10378</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>935</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>813</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3604</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>7477</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>947</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1465</t>
+          <t>1400</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1890; 8942</t>
+          <t>0; 4035</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2841; 10483</t>
+          <t>1285; 8010</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6208; 16537</t>
+          <t>3552; 12959</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 5357</t>
+          <t>0; 2620</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4227</t>
+          <t>2053; 9673</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1271; 7992</t>
+          <t>2931; 10975</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4004; 13121</t>
+          <t>6111; 16051</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 2895</t>
+          <t>0; 5157</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2813; 10605</t>
+          <t>2542; 10345</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5239; 15522</t>
+          <t>5466; 15457</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11739; 25377</t>
+          <t>11559; 26099</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 5632</t>
+          <t>0; 4870</t>
         </is>
       </c>
     </row>
@@ -2905,42 +2905,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>5205</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4963</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1883</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2926</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>3432</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>4328</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>628</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3588</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>5205</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>4963</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>1883</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>3833</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6404</t>
+          <t>6759</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1322; 6942</t>
+          <t>2357; 9576</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1447; 8831</t>
+          <t>2128; 9560</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3804</t>
+          <t>597; 5001</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1535; 7042</t>
+          <t>1065; 6318</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2149; 9506</t>
+          <t>1301; 7656</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2018; 8895</t>
+          <t>1526; 8914</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>601; 5055</t>
+          <t>0; 3350</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1023; 5942</t>
+          <t>1676; 7146</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4836; 14906</t>
+          <t>4826; 14044</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5524; 15466</t>
+          <t>5122; 15525</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>619; 5836</t>
+          <t>618; 5808</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3588; 10856</t>
+          <t>3649; 11227</t>
         </is>
       </c>
     </row>
@@ -3113,37 +3113,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5181</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>6823</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3161</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1389</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>2942</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>6669</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2060</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>5181</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>6823</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>3161</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1794</t>
+          <t>2133</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3855</t>
+          <t>3522</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>635; 5428</t>
+          <t>1994; 9220</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>735; 7094</t>
+          <t>3428; 12456</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3533; 12099</t>
+          <t>794; 7107</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>619; 5592</t>
+          <t>243; 4316</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2208; 9453</t>
+          <t>632; 5362</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3542; 11870</t>
+          <t>750; 7430</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>778; 7142</t>
+          <t>3496; 12264</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>360; 5368</t>
+          <t>682; 6170</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3912; 12434</t>
+          <t>3913; 12647</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5634; 16089</t>
+          <t>5029; 16022</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5356; 16017</t>
+          <t>5367; 16015</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1387; 8046</t>
+          <t>1262; 7422</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>8858</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>7216</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2381</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>12585</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>4986</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>6730</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>5400</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>11924</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>8858</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>7216</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>2381</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>13175</t>
+          <t>12278</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>25099</t>
+          <t>24863</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2094; 9493</t>
+          <t>4751; 14268</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3031; 11835</t>
+          <t>3468; 14696</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2506; 10367</t>
+          <t>644; 6493</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6535; 18397</t>
+          <t>6966; 19869</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4744; 15304</t>
+          <t>2126; 9910</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3192; 12598</t>
+          <t>3332; 12424</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>655; 6740</t>
+          <t>2504; 10455</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>6924; 21737</t>
+          <t>7497; 18443</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8779; 21069</t>
+          <t>8841; 21162</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8774; 21689</t>
+          <t>8505; 21066</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4104; 13029</t>
+          <t>3776; 13199</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>17367; 35521</t>
+          <t>16629; 34453</t>
         </is>
       </c>
     </row>
@@ -3529,37 +3529,37 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>14743</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>7901</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>6876</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2399</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>13501</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>6251</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>7989</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>2384</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>14743</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>7901</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>6876</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2465</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>5037</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>8545; 20101</t>
+          <t>9517; 21558</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3157; 10740</t>
+          <t>4126; 13070</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4254; 13778</t>
+          <t>3554; 12298</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>740; 6434</t>
+          <t>626; 6690</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>10162; 22248</t>
+          <t>8767; 19944</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4536; 13391</t>
+          <t>3082; 11058</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3440; 12130</t>
+          <t>4467; 13542</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>713; 6707</t>
+          <t>0; 7109</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>20657; 37701</t>
+          <t>20713; 37070</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>9017; 21007</t>
+          <t>8941; 20142</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>9938; 22333</t>
+          <t>9864; 22229</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2139; 9944</t>
+          <t>1795; 10393</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>54</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>49879</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>48684</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>33716</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>34294</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>45821</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>36672</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>40933</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>38849</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>49879</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>48684</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>33716</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>37518</t>
+          <t>38281</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>76367</t>
+          <t>72575</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>36410; 58466</t>
+          <t>40464; 63034</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>28359; 47592</t>
+          <t>37611; 60864</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>31165; 52117</t>
+          <t>25408; 43923</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>28474; 50197</t>
+          <t>24835; 46040</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>40242; 62884</t>
+          <t>35874; 57442</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>38542; 60200</t>
+          <t>27318; 46356</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25286; 44593</t>
+          <t>31333; 51664</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>27386; 49894</t>
+          <t>28520; 49187</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>81343; 110831</t>
+          <t>81953; 111232</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>71872; 103048</t>
+          <t>71434; 100916</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>61321; 89220</t>
+          <t>61818; 89187</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>61602; 92702</t>
+          <t>59739; 89200</t>
         </is>
       </c>
     </row>
